--- a/outputs/42198.xlsx
+++ b/outputs/42198.xlsx
@@ -122,16 +122,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -399,79 +403,79 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="b">
+      <c r="B2" s="3" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="C2" s="0" t="str">
-        <f aca="false">IF(COUNTIFS($A$2:A2,"Potato",$B$2:B2,FALSE())&gt;0,"Worst",IF(COUNTIFS($A$2:A2,"Tomato",$B$2:B2,FALSE())&gt;0,"Ignore",IF(COUNTIFS($A$2:A2,"Pickle",$B$2:B2,FALSE())&gt;0,"Bad","Good")))</f>
+      <c r="C2" s="2" t="str">
+        <f aca="false">IF(COUNTIFS(A$2:A2,"Potato",B$2:B2,FALSE())&gt;0,"Worst",IF(COUNTIFS(A$2:A2,"Tomato",B$2:B2,FALSE())&gt;0,"Ignore",IF(COUNTIFS(A$2:A2,"Pickle",B$2:B2,FALSE())&gt;0,"Bad","Good")))</f>
         <v>Good</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="b">
+      <c r="B3" s="3" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="C3" s="0" t="str">
-        <f aca="false">IF(COUNTIFS($A$2:A3,"Potato",$B$2:B3,FALSE())&gt;0,"Worst",IF(COUNTIFS($A$2:A3,"Tomato",$B$2:B3,FALSE())&gt;0,"Ignore",IF(COUNTIFS($A$2:A3,"Pickle",$B$2:B3,FALSE())&gt;0,"Bad","Good")))</f>
+      <c r="C3" s="2" t="str">
+        <f aca="false">IF(COUNTIFS(A$2:A3,"Potato",B$2:B3,FALSE())&gt;0,"Worst",IF(COUNTIFS(A$2:A3,"Tomato",B$2:B3,FALSE())&gt;0,"Ignore",IF(COUNTIFS(A$2:A3,"Pickle",B$2:B3,FALSE())&gt;0,"Bad","Good")))</f>
         <v>Good</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="0" t="str">
-        <f aca="false">IF(COUNTIFS($A$2:A4,"Potato",$B$2:B4,FALSE())&gt;0,"Worst",IF(COUNTIFS($A$2:A4,"Tomato",$B$2:B4,FALSE())&gt;0,"Ignore",IF(COUNTIFS($A$2:A4,"Pickle",$B$2:B4,FALSE())&gt;0,"Bad","Good")))</f>
+      <c r="C4" s="2" t="str">
+        <f aca="false">IF(COUNTIFS(A$2:A4,"Potato",B$2:B4,FALSE())&gt;0,"Worst",IF(COUNTIFS(A$2:A4,"Tomato",B$2:B4,FALSE())&gt;0,"Ignore",IF(COUNTIFS(A$2:A4,"Pickle",B$2:B4,FALSE())&gt;0,"Bad","Good")))</f>
         <v>Good</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="2" t="b">
+      <c r="B5" s="3" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="C5" s="0" t="str">
-        <f aca="false">IF(COUNTIFS($A$2:A5,"Potato",$B$2:B5,FALSE())&gt;0,"Worst",IF(COUNTIFS($A$2:A5,"Tomato",$B$2:B5,FALSE())&gt;0,"Ignore",IF(COUNTIFS($A$2:A5,"Pickle",$B$2:B5,FALSE())&gt;0,"Bad","Good")))</f>
+      <c r="C5" s="2" t="str">
+        <f aca="false">IF(COUNTIFS(A$2:A5,"Potato",B$2:B5,FALSE())&gt;0,"Worst",IF(COUNTIFS(A$2:A5,"Tomato",B$2:B5,FALSE())&gt;0,"Ignore",IF(COUNTIFS(A$2:A5,"Pickle",B$2:B5,FALSE())&gt;0,"Bad","Good")))</f>
         <v>Bad</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="2" t="b">
+      <c r="B6" s="3" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="C6" s="0" t="str">
-        <f aca="false">IF(COUNTIFS($A$2:A6,"Potato",$B$2:B6,FALSE())&gt;0,"Worst",IF(COUNTIFS($A$2:A6,"Tomato",$B$2:B6,FALSE())&gt;0,"Ignore",IF(COUNTIFS($A$2:A6,"Pickle",$B$2:B6,FALSE())&gt;0,"Bad","Good")))</f>
+      <c r="C6" s="2" t="str">
+        <f aca="false">IF(COUNTIFS(A$2:A6,"Potato",B$2:B6,FALSE())&gt;0,"Worst",IF(COUNTIFS(A$2:A6,"Tomato",B$2:B6,FALSE())&gt;0,"Ignore",IF(COUNTIFS(A$2:A6,"Pickle",B$2:B6,FALSE())&gt;0,"Bad","Good")))</f>
         <v>Bad</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="2" t="b">
+      <c r="B7" s="3" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
-      <c r="C7" s="0" t="str">
-        <f aca="false">IF(COUNTIFS($A$2:A7,"Potato",$B$2:B7,FALSE())&gt;0,"Worst",IF(COUNTIFS($A$2:A7,"Tomato",$B$2:B7,FALSE())&gt;0,"Ignore",IF(COUNTIFS($A$2:A7,"Pickle",$B$2:B7,FALSE())&gt;0,"Bad","Good")))</f>
+      <c r="C7" s="2" t="str">
+        <f aca="false">IF(COUNTIFS(A$2:A7,"Potato",B$2:B7,FALSE())&gt;0,"Worst",IF(COUNTIFS(A$2:A7,"Tomato",B$2:B7,FALSE())&gt;0,"Ignore",IF(COUNTIFS(A$2:A7,"Pickle",B$2:B7,FALSE())&gt;0,"Bad","Good")))</f>
         <v>Bad</v>
       </c>
     </row>

--- a/outputs/42198.xlsx
+++ b/outputs/42198.xlsx
@@ -122,7 +122,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -132,10 +132,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -391,7 +387,7 @@
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -402,33 +398,33 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="3" t="b">
+      <c r="B2" s="2" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="C2" s="2" t="str">
-        <f aca="false">IF(COUNTIFS(A$2:A2,"Potato",B$2:B2,FALSE())&gt;0,"Worst",IF(COUNTIFS(A$2:A2,"Tomato",B$2:B2,FALSE())&gt;0,"Ignore",IF(COUNTIFS(A$2:A2,"Pickle",B$2:B2,FALSE())&gt;0,"Bad","Good")))</f>
+        <f aca="false">IF(SUMPRODUCT(($A$2="Potato")*($B$2=FALSE()))&gt;0,"Worst",IF(SUMPRODUCT(($A$2="Tomato")*($B$2=FALSE()))&gt;0,"Ignore",IF(SUMPRODUCT(($A$2="Pickle")*($B$2=FALSE()))&gt;0,"Bad","Good")))</f>
         <v>Good</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="b">
+      <c r="B3" s="2" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="C3" s="2" t="str">
-        <f aca="false">IF(COUNTIFS(A$2:A3,"Potato",B$2:B3,FALSE())&gt;0,"Worst",IF(COUNTIFS(A$2:A3,"Tomato",B$2:B3,FALSE())&gt;0,"Ignore",IF(COUNTIFS(A$2:A3,"Pickle",B$2:B3,FALSE())&gt;0,"Bad","Good")))</f>
+        <f aca="false">IF(SUMPRODUCT(($A$2:$A$3="Potato")*($B$2:$B$3=FALSE()))&gt;0,"Worst",IF(SUMPRODUCT(($A$2:$A$3="Tomato")*($B$2:$B$3=FALSE()))&gt;0,"Ignore",IF(SUMPRODUCT(($A$2:$A$3="Pickle")*($B$2:$B$3=FALSE()))&gt;0,"Bad","Good")))</f>
         <v>Good</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -436,46 +432,46 @@
         <v>5</v>
       </c>
       <c r="C4" s="2" t="str">
-        <f aca="false">IF(COUNTIFS(A$2:A4,"Potato",B$2:B4,FALSE())&gt;0,"Worst",IF(COUNTIFS(A$2:A4,"Tomato",B$2:B4,FALSE())&gt;0,"Ignore",IF(COUNTIFS(A$2:A4,"Pickle",B$2:B4,FALSE())&gt;0,"Bad","Good")))</f>
+        <f aca="false">IF(SUMPRODUCT(($A$2:$A$4="Potato")*($B$2:$B$4=FALSE()))&gt;0,"Worst",IF(SUMPRODUCT(($A$2:$A$4="Tomato")*($B$2:$B$4=FALSE()))&gt;0,"Ignore",IF(SUMPRODUCT(($A$2:$A$4="Pickle")*($B$2:$B$4=FALSE()))&gt;0,"Bad","Good")))</f>
         <v>Good</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="3" t="b">
+      <c r="B5" s="2" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="C5" s="2" t="str">
-        <f aca="false">IF(COUNTIFS(A$2:A5,"Potato",B$2:B5,FALSE())&gt;0,"Worst",IF(COUNTIFS(A$2:A5,"Tomato",B$2:B5,FALSE())&gt;0,"Ignore",IF(COUNTIFS(A$2:A5,"Pickle",B$2:B5,FALSE())&gt;0,"Bad","Good")))</f>
+        <f aca="false">IF(SUMPRODUCT(($A$2:$A$5="Potato")*($B$2:$B$5=FALSE()))&gt;0,"Worst",IF(SUMPRODUCT(($A$2:$A$5="Tomato")*($B$2:$B$5=FALSE()))&gt;0,"Ignore",IF(SUMPRODUCT(($A$2:$A$5="Pickle")*($B$2:$B$5=FALSE()))&gt;0,"Bad","Good")))</f>
         <v>Bad</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="3" t="b">
+      <c r="B6" s="2" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="C6" s="2" t="str">
-        <f aca="false">IF(COUNTIFS(A$2:A6,"Potato",B$2:B6,FALSE())&gt;0,"Worst",IF(COUNTIFS(A$2:A6,"Tomato",B$2:B6,FALSE())&gt;0,"Ignore",IF(COUNTIFS(A$2:A6,"Pickle",B$2:B6,FALSE())&gt;0,"Bad","Good")))</f>
+        <f aca="false">IF(SUMPRODUCT(($A$2:$A$6="Potato")*($B$2:$B$6=FALSE()))&gt;0,"Worst",IF(SUMPRODUCT(($A$2:$A$6="Tomato")*($B$2:$B$6=FALSE()))&gt;0,"Ignore",IF(SUMPRODUCT(($A$2:$A$6="Pickle")*($B$2:$B$6=FALSE()))&gt;0,"Bad","Good")))</f>
         <v>Bad</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="3" t="b">
+      <c r="B7" s="2" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="C7" s="2" t="str">
-        <f aca="false">IF(COUNTIFS(A$2:A7,"Potato",B$2:B7,FALSE())&gt;0,"Worst",IF(COUNTIFS(A$2:A7,"Tomato",B$2:B7,FALSE())&gt;0,"Ignore",IF(COUNTIFS(A$2:A7,"Pickle",B$2:B7,FALSE())&gt;0,"Bad","Good")))</f>
+        <f aca="false">IF(SUMPRODUCT(($A$2:$A$7="Potato")*($B$2:$B$7=FALSE()))&gt;0,"Worst",IF(SUMPRODUCT(($A$2:$A$7="Tomato")*($B$2:$B$7=FALSE()))&gt;0,"Ignore",IF(SUMPRODUCT(($A$2:$A$7="Pickle")*($B$2:$B$7=FALSE()))&gt;0,"Bad","Good")))</f>
         <v>Bad</v>
       </c>
     </row>
